--- a/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor</t>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,66; 47,72</t>
+          <t>20,01; 48,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 23,45</t>
+          <t>3,56; 24,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,05; 31,28</t>
+          <t>12,89; 29,94</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 46,66</t>
+          <t>19,06; 46,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 42,5</t>
+          <t>22,09; 43,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 41,38</t>
+          <t>25,01; 40,93</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 53,4</t>
+          <t>10,21; 52,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,89; 57,09</t>
+          <t>30,43; 57,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,76; 49,99</t>
+          <t>20,29; 50,1</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 41,13</t>
+          <t>17,82; 43,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 45,04</t>
+          <t>18,58; 46,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 39,22</t>
+          <t>21,04; 40,45</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,31; 40,24</t>
+          <t>18,84; 40,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 39,1</t>
+          <t>26,39; 39,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 36,15</t>
+          <t>23,81; 36,94</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11686</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5391; 13023</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1002; 6809</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7103; 16501</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14967</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20301</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35268</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8533; 20920</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14096; 27781</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27156; 44448</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>24489</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49676</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7871; 40748</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17320; 32580</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27189; 67134</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8774</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10169</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18943</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5446; 13254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6282; 15558</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13544; 26038</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>115574</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33793; 72844</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>48224; 71335</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>86219; 133730</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 48,34</t>
+          <t>19,33; 49,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 24,18</t>
+          <t>3,61; 21,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 29,94</t>
+          <t>13,44; 31,82</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 46,72</t>
+          <t>20,2; 47,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 43,54</t>
+          <t>22,3; 42,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,01; 40,93</t>
+          <t>24,36; 41,07</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 52,87</t>
+          <t>11,13; 53,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,43; 57,23</t>
+          <t>31,29; 56,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,29; 50,1</t>
+          <t>18,44; 49,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 43,37</t>
+          <t>16,94; 43,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 46,02</t>
+          <t>16,26; 44,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 40,45</t>
+          <t>20,74; 40,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 40,62</t>
+          <t>19,91; 40,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 39,04</t>
+          <t>26,16; 38,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,94</t>
+          <t>24,88; 37,03</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5391; 13023</t>
+          <t>5207; 13435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1002; 6809</t>
+          <t>1017; 6188</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7103; 16501</t>
+          <t>7405; 17536</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8533; 20920</t>
+          <t>9045; 21320</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14096; 27781</t>
+          <t>14229; 27250</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27156; 44448</t>
+          <t>26453; 44597</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7871; 40748</t>
+          <t>8577; 41233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17320; 32580</t>
+          <t>17812; 32362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27189; 67134</t>
+          <t>24709; 66633</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5446; 13254</t>
+          <t>5176; 13205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6282; 15558</t>
+          <t>5498; 14898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13544; 26038</t>
+          <t>13349; 25889</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33793; 72844</t>
+          <t>35717; 73114</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48224; 71335</t>
+          <t>47794; 69961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86219; 133730</t>
+          <t>90094; 134078</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 49,87</t>
+          <t>3,75; 25,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 21,97</t>
+          <t>20,9; 49,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,44; 31,82</t>
+          <t>15,2; 33,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,2; 47,61</t>
+          <t>21,5; 42,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,3; 42,71</t>
+          <t>23,47; 49,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,36; 41,07</t>
+          <t>25,34; 42,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 53,5</t>
+          <t>27,61; 54,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,29; 56,85</t>
+          <t>36,14; 61,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 49,73</t>
+          <t>35,72; 55,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 43,21</t>
+          <t>18,37; 47,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,26; 44,07</t>
+          <t>16,55; 42,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 40,22</t>
+          <t>21,65; 40,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 40,77</t>
+          <t>25,79; 38,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,16; 38,29</t>
+          <t>32,78; 45,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 37,03</t>
+          <t>30,14; 39,27</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12232</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5207; 13435</t>
+          <t>944; 6518</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1017; 6188</t>
+          <t>5724; 13684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7405; 17536</t>
+          <t>7982; 17793</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>31269</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9045; 21320</t>
+          <t>12140; 24179</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14229; 27250</t>
+          <t>8617; 18276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26453; 44597</t>
+          <t>23607; 39296</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>46434</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8577; 41233</t>
+          <t>14453; 28527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17812; 32362</t>
+          <t>18371; 31023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24709; 66633</t>
+          <t>36857; 57406</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19121</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5176; 13205</t>
+          <t>5789; 15065</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5498; 14898</t>
+          <t>4920; 12733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13349; 25889</t>
+          <t>13260; 25074</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35717; 73114</t>
+          <t>42683; 63754</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47794; 69961</t>
+          <t>47419; 66158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90094; 134078</t>
+          <t>93456; 121778</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34,57%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,75; 25,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20,9; 49,98</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15,2; 33,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>21,5; 42,83</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23,47; 49,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25,34; 42,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,61; 54,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36,14; 61,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35,72; 55,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29,66%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>18,37; 47,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16,55; 42,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21,65; 40,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>25,79; 38,53</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32,78; 45,74</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30,14; 39,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.11003015319067</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3456532995474831</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2328503675146784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2767</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9465</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12232</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.03753469515680736</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.2090374996678339</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1519550734935392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>944; 6518</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5724; 13684</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7982; 17793</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2591899537069827</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.4997607783689554</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3387151140584407</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3164823527639837</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3650491670194982</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3356187282885241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>17868</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13401</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31269</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2150209370835881</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.2347261657755864</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2533795751693213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12140; 24179</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8617; 18276</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23607; 39296</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4282728192106334</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4978405671305192</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4217796106945657</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4185302272635139</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4824737918335484</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4500281709000387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21912</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24522</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46434</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2760586921900006</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.361442279832227</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3572105240424157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>14453; 28527</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18371; 31023</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36857; 57406</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5448723881610229</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6103802216437331</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5563650290697674</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3269526214805035</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2966065413790798</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3122241438357041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10305</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8816</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19121</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1836790835151694</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1655317733398203</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2165307496414595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>5789; 15065</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4920; 12733</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13260; 25074</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4780101710364385</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4283741706924047</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4094455289913589</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.3193876990993028</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3885750505526774</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3516569265573155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>52852</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>56204</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109056</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.2579387873970066</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.3278366154360199</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.301353385107934</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>42683; 63754</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>47419; 66158</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>93456; 121778</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3852719095209731</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4573913188523958</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3926786971843211</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2767</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9465</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>12232</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>944</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5724</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6518</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>13684</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>17793</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17868</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>13401</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>31269</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12140</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>8617</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>23607</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>24179</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18276</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>39296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>21912</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>24522</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>46434</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>14453</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>18371</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>36857</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>28527</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>31023</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>57406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>10305</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>8816</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>19121</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5789</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4920</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>13260</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>15065</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>12733</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>25074</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>52852</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>56204</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>109056</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>42683</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>47419</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>93456</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>63754</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>66158</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>121778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>